--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486375_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486375_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3565</v>
+        <v>6.8518</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1673</v>
+        <v>4.279</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1892</v>
+        <v>2.5727</v>
       </c>
       <c r="G2" t="n">
         <v>4.7055</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9109</v>
+        <v>0.4062</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4588</v>
+        <v>0.8424</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5451</v>
+        <v>3.4719</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2475</v>
+        <v>3.3627</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7024</v>
+        <v>0.1092</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1183</v>
+        <v>4.0022</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0427</v>
+        <v>0.0243</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.161</v>
+        <v>3.9779</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8844</v>
+        <v>6.5388</v>
       </c>
       <c r="K3" t="n">
-        <v>1.156</v>
+        <v>1.3536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7284</v>
+        <v>5.1852</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0027</v>
+        <v>-2.5366</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1134</v>
+        <v>-1.3293</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8893</v>
+        <v>-1.2073</v>
       </c>
       <c r="P3" t="n">
-        <v>1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2175</v>
+        <v>-4.7852</v>
       </c>
       <c r="R3" t="n">
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7933</v>
+        <v>0.8421</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7557</v>
+        <v>-0.2812</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0377</v>
+        <v>1.1233</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.8902</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8249</v>
+        <v>1.8902</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2154</v>
+        <v>3.1869</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8904</v>
+        <v>5.0434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.325</v>
+        <v>-1.8565</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0022</v>
+        <v>-0.1183</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0243</v>
+        <v>0.0427</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9779</v>
+        <v>-0.161</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5388</v>
+        <v>1.8844</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3536</v>
+        <v>1.156</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1852</v>
+        <v>0.7284</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5366</v>
+        <v>-2.0027</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3293</v>
+        <v>-1.1134</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2073</v>
+        <v>-0.8893</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.2626</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.7852</v>
+        <v>-0.2175</v>
       </c>
       <c r="R4" t="n">
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5856</v>
+        <v>1.4351</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="U4" t="n">
-        <v>1.339</v>
+        <v>0.8835</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8902</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8902</v>
+        <v>2.8249</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1033</v>
+        <v>2.5871</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1582</v>
+        <v>1.5187</v>
       </c>
       <c r="F5" t="n">
-        <v>0.945</v>
+        <v>1.0683</v>
       </c>
       <c r="G5" t="n">
         <v>4.0712</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0103</v>
+        <v>0.4735</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8904</v>
+        <v>-0.5299</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8801</v>
+        <v>1.0034</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9234</v>
+        <v>2.1276</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6359</v>
+        <v>0.7477</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2874</v>
+        <v>1.3799</v>
       </c>
       <c r="G6" t="n">
         <v>1.4712</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9574</v>
+        <v>-0.7532</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9589</v>
+        <v>-0.8472</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0016</v>
+        <v>0.094</v>
       </c>
       <c r="V6" t="n">
         <v>-0.113</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6734</v>
+        <v>1.7543</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2483</v>
+        <v>1.36</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4251</v>
+        <v>0.3943</v>
       </c>
       <c r="G7" t="n">
         <v>2.85</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1936</v>
+        <v>-0.1127</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2174</v>
+        <v>0.1866</v>
       </c>
       <c r="V7" t="n">
         <v>-0.113</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4525</v>
+        <v>1.4585</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0645</v>
+        <v>0.9976</v>
       </c>
       <c r="F8" t="n">
-        <v>1.388</v>
+        <v>0.4609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6373</v>
+        <v>1.1614</v>
       </c>
       <c r="H8" t="n">
-        <v>0.152</v>
+        <v>-2.8771</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4853</v>
+        <v>4.0385</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0747</v>
+        <v>2.8326</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0365</v>
+        <v>-1.7972</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>4.6298</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5626</v>
+        <v>-1.6712</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1155</v>
+        <v>-1.0799</v>
       </c>
       <c r="O8" t="n">
-        <v>0.447</v>
+        <v>-0.5913</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0326</v>
+        <v>0.2971</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2055</v>
+        <v>-0.5299</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1729</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.87</v>
+        <v>1.4217</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2681</v>
+        <v>0.0645</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3981</v>
+        <v>1.3572</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0291</v>
+        <v>0.6373</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2403</v>
+        <v>0.152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2694</v>
+        <v>0.4853</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1416</v>
+        <v>0.0747</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9886</v>
+        <v>0.0365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.153</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1707</v>
+        <v>0.5626</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7484</v>
+        <v>0.1155</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4224</v>
+        <v>0.447</v>
       </c>
       <c r="P9" t="n">
         <v>0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0309</v>
+        <v>-0.0634</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9589</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9281</v>
+        <v>0.1421</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2775</v>
+        <v>0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5204</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.759</v>
+        <v>1.0147</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6371</v>
+        <v>1.6286</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1219</v>
+        <v>-0.6139</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1614</v>
+        <v>-0.0291</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8771</v>
+        <v>0.2403</v>
       </c>
       <c r="I10" t="n">
-        <v>4.0385</v>
+        <v>-0.2694</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8326</v>
+        <v>1.1416</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7972</v>
+        <v>0.9886</v>
       </c>
       <c r="L10" t="n">
-        <v>4.6298</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6712</v>
+        <v>-1.1707</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0799</v>
+        <v>-0.7484</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5913</v>
+        <v>-0.4224</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4024</v>
+        <v>0.1139</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8904</v>
+        <v>-0.5984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.488</v>
+        <v>0.7123</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2775</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2628</v>
+        <v>0.4169</v>
       </c>
       <c r="E11" t="n">
         <v>-0.2375</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5003</v>
+        <v>0.6544</v>
       </c>
       <c r="G11" t="n">
         <v>0.5145999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4693</v>
+        <v>-0.3151</v>
       </c>
       <c r="T11" t="n">
         <v>-0.274</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1953</v>
+        <v>-0.0412</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3094</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>-2.4775</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1682</v>
+        <v>2.4147</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1053</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0481</v>
+        <v>-0.8015</v>
       </c>
       <c r="T12" t="n">
         <v>-0.9589</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0892</v>
+        <v>0.1574</v>
       </c>
       <c r="V12" t="n">
         <v>0.6264999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1113</v>
+        <v>-2.803</v>
       </c>
       <c r="E13" t="n">
         <v>-3.3039</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1927</v>
+        <v>0.5009</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2278</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6405</v>
+        <v>-0.3323</v>
       </c>
       <c r="T13" t="n">
         <v>-0.548</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0925</v>
+        <v>0.2157</v>
       </c>
       <c r="V13" t="n">
         <v>-0.113</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.7407</v>
+        <v>21.4256</v>
       </c>
       <c r="E14" t="n">
-        <v>12.2984</v>
+        <v>12.9833</v>
       </c>
       <c r="F14" t="n">
-        <v>8.442300000000001</v>
+        <v>8.4421</v>
       </c>
       <c r="G14" t="n">
         <v>15.9329</v>
@@ -1528,7 +1528,7 @@
         <v>17.9336</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.149300000000002</v>
+        <v>-9.1493</v>
       </c>
       <c r="N14" t="n">
         <v>-5.2487</v>
@@ -1537,7 +1537,7 @@
         <v>-3.901</v>
       </c>
       <c r="P14" t="n">
-        <v>1.087399999999999</v>
+        <v>1.0874</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.1379</v>
@@ -1546,13 +1546,13 @@
         <v>15.2252</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5047000000000003</v>
+        <v>1.1897</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.6418</v>
+        <v>-4.9568</v>
       </c>
       <c r="U14" t="n">
-        <v>6.1466</v>
+        <v>6.146599999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.2154</v>
@@ -1561,7 +1561,7 @@
         <v>6.995699999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.780400000000001</v>
+        <v>-3.7804</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3412</v>
+        <v>5.2718</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4685</v>
+        <v>3.245</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8727</v>
+        <v>2.0269</v>
       </c>
       <c r="G15" t="n">
         <v>3.1801</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5738</v>
+        <v>0.5044</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1334</v>
+        <v>-0.3569</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.8613</v>
       </c>
       <c r="V15" t="n">
         <v>0.9347</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3703</v>
+        <v>1.696</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1702</v>
+        <v>-0.165</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2001</v>
+        <v>1.861</v>
       </c>
       <c r="G16" t="n">
         <v>2.3224</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.353</v>
+        <v>0.6787</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1334</v>
+        <v>-0.4687</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4864</v>
+        <v>1.1473</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1041</v>
+        <v>0.0771</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.2706</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0394</v>
+        <v>-0.1935</v>
       </c>
       <c r="G17" t="n">
         <v>-2.2753</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2638</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3699</v>
+        <v>-1.0346</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1061</v>
+        <v>0.952</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.921</v>
+        <v>-0.8759</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6173</v>
+        <v>-0.4871</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6963</v>
+        <v>-0.3888</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6181</v>
+        <v>-1.5455</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4959</v>
+        <v>-0.0092</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.114</v>
+        <v>-1.5363</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5263</v>
+        <v>-0.2131</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8458</v>
+        <v>0.0912</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3721</v>
+        <v>-0.3044</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0917</v>
+        <v>-1.3324</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3499</v>
+        <v>-0.1004</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2582</v>
+        <v>-1.232</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9146</v>
+        <v>-0.2004</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1334</v>
+        <v>-0.274</v>
       </c>
       <c r="U18" t="n">
-        <v>1.048</v>
+        <v>0.0736</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9684</v>
+        <v>-0.8949</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4871</v>
+        <v>-1.0749</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4812</v>
+        <v>0.18</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5455</v>
+        <v>0.3006</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0092</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5363</v>
+        <v>-0.3259</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2131</v>
+        <v>1.1398</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0912</v>
+        <v>1.0434</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3044</v>
+        <v>0.0964</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3324</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1004</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.232</v>
+        <v>-0.4224</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2929</v>
+        <v>0.152</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.274</v>
+        <v>-0.6922</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0189</v>
+        <v>0.8442</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1685</v>
+        <v>-0.9368</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4102</v>
+        <v>2.5614</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2417</v>
+        <v>-3.4982</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3006</v>
+        <v>-1.5006</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6264999999999999</v>
+        <v>-1.2408</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3259</v>
+        <v>-0.2598</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1398</v>
+        <v>3.7086</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0434</v>
+        <v>-0.1944</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0964</v>
+        <v>3.903</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-5.2092</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4169</v>
+        <v>-1.0464</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4224</v>
+        <v>-4.1628</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5225</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1216</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0274</v>
+        <v>-0.9722</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9058</v>
+        <v>0.3184</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1718</v>
+        <v>-1.1137</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4497</v>
+        <v>-1.8408</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6215</v>
+        <v>0.7271</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5006</v>
+        <v>-0.6181</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2408</v>
+        <v>0.4959</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2598</v>
+        <v>-1.114</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7086</v>
+        <v>-0.5263</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1944</v>
+        <v>0.8458</v>
       </c>
       <c r="L21" t="n">
-        <v>3.903</v>
+        <v>-1.3721</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.2092</v>
+        <v>-0.0917</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0464</v>
+        <v>-0.3499</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.1628</v>
+        <v>0.2582</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-1.5225</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8888</v>
+        <v>0.7219</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0839</v>
+        <v>-0.3569</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1952</v>
+        <v>1.0788</v>
       </c>
       <c r="V21" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0002</v>
+        <v>-2.0426</v>
       </c>
       <c r="E22" t="n">
-        <v>0.725</v>
+        <v>0.8368</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7252</v>
+        <v>-2.8794</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4092</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5681</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.6862</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2722</v>
+        <v>0.1181</v>
       </c>
       <c r="V22" t="n">
         <v>0.3698</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6016</v>
+        <v>-4.459</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7388</v>
+        <v>-0.627</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8628</v>
+        <v>-3.832</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3932</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2534</v>
+        <v>-0.1109</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.125</v>
+        <v>-0.0132</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8249</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3364</v>
+        <v>-5.1938</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1977</v>
+        <v>-3.086</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1387</v>
+        <v>-2.1079</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4305</v>
@@ -2326,13 +2326,13 @@
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6884</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8904</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.202</v>
+        <v>0.2328</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>J. DAVIS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9797</v>
+        <v>-6.027</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7155</v>
+        <v>-2.9127</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2643</v>
+        <v>-3.1143</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.0463</v>
+        <v>-5.5174</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4621</v>
+        <v>-2.6184</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5842</v>
+        <v>-2.899</v>
       </c>
       <c r="J25" t="n">
-        <v>0.08459999999999999</v>
+        <v>-2.557</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0302</v>
+        <v>-1.8884</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1147</v>
+        <v>-0.6686</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1309</v>
+        <v>-2.9604</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.432</v>
+        <v>-0.73</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.6989</v>
+        <v>-2.2304</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.2626</v>
+        <v>0.6525</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2639</v>
+        <v>-0.402</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2896</v>
+        <v>-0.3557</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0257</v>
+        <v>-0.0463</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9347</v>
+        <v>-0.7602</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. DAVIS</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.2004</v>
+        <v>-6.2418</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0244</v>
+        <v>-5.1625</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.176</v>
+        <v>-1.0793</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.5174</v>
+        <v>-2.0463</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6184</v>
+        <v>-0.4621</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.899</v>
+        <v>-1.5842</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.557</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.8884</v>
+        <v>-0.0302</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6686</v>
+        <v>0.1147</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.9604</v>
+        <v>-2.1309</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.73</v>
+        <v>-0.432</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.2304</v>
+        <v>-1.6989</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6525</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5754</v>
+        <v>0.0018</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4675</v>
+        <v>-0.1574</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1079</v>
+        <v>0.1592</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7602</v>
+        <v>-0.9347</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="27">
@@ -2518,10 +2518,10 @@
         <v>-20.7406</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.442299999999999</v>
+        <v>-8.4422</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.2983</v>
+        <v>-12.2984</v>
       </c>
       <c r="G27" t="n">
         <v>-15.933</v>
@@ -2560,13 +2560,13 @@
         <v>14.1378</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5046999999999995</v>
+        <v>-0.5048</v>
       </c>
       <c r="T27" t="n">
-        <v>-6.1466</v>
+        <v>-6.146699999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>5.641900000000001</v>
+        <v>5.6418</v>
       </c>
       <c r="V27" t="n">
         <v>-3.2153</v>
